--- a/cadastro_condominios.xlsx
+++ b/cadastro_condominios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Condominios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condominios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,12 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C758"/>
+  <dimension ref="A1:D758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,6 +438,11 @@
           <t>Nome do Condomínio</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ID SL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,6 +460,11 @@
           <t>29 DE JUNHO</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,6 +482,11 @@
           <t>ABATODA</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -488,6 +504,11 @@
           <t>ACALANTO</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -505,6 +526,11 @@
           <t>ACARA</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -522,6 +548,11 @@
           <t>ACRON</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -539,6 +570,11 @@
           <t>ACVPAN</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -556,6 +592,11 @@
           <t>ADMIRAL</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -573,6 +614,11 @@
           <t>ADOLFO LUTZ</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -590,6 +636,11 @@
           <t>AGULHAS NEGRAS</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -607,6 +658,11 @@
           <t>ALAYDE</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -624,6 +680,11 @@
           <t>ALBERT SABIN</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -641,6 +702,11 @@
           <t>ALCIO SOUTO</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -658,6 +724,11 @@
           <t>ALESSANDRA</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -675,6 +746,11 @@
           <t>ALEXANDRE</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -692,6 +768,11 @@
           <t>ALFREDO DE MATTOS</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -709,6 +790,11 @@
           <t>ALGARVIO</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -726,6 +812,11 @@
           <t>ALIRIO BRAZ</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -743,6 +834,11 @@
           <t>ALMIRANTE BALTHAZAR</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -760,6 +856,11 @@
           <t>ALMIRANTE COCHRANE</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -777,6 +878,11 @@
           <t>ALMTE JOSE VICTOR DELAMARE</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -794,6 +900,11 @@
           <t>ALVAREZ</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -811,6 +922,11 @@
           <t>ALVORADA</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -828,6 +944,11 @@
           <t>AMAHU - ASSOC MOR.E A. HUMAITA</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -845,6 +966,11 @@
           <t>AMAROSAS</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -862,6 +988,11 @@
           <t>AMAVIL - VIUVA LACERDA</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -879,6 +1010,11 @@
           <t>AMMAS</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -896,6 +1032,11 @@
           <t>AMORA</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -913,6 +1054,11 @@
           <t>AMORIM</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -930,6 +1076,11 @@
           <t>AMPERE</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -947,6 +1098,11 @@
           <t>ANA CRISTINA</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -964,6 +1120,11 @@
           <t>ANA FRANCISCA</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -981,6 +1142,11 @@
           <t>ANA GABRIELA</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -998,6 +1164,11 @@
           <t>ANA MARIA CESAR</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1015,6 +1186,11 @@
           <t>ANA PAULA</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1032,6 +1208,11 @@
           <t>ANALUCIA</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1049,6 +1230,11 @@
           <t>ANAÍS</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1066,6 +1252,11 @@
           <t>ANDALUZIA</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1083,6 +1274,11 @@
           <t>ANGE BLANC</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1100,6 +1296,11 @@
           <t>ANGELO AGOSTINI</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1117,6 +1318,11 @@
           <t>ANGRENSE</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1134,6 +1340,11 @@
           <t>ANTONIETA</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1151,6 +1362,11 @@
           <t>APART HOTEL</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1168,6 +1384,11 @@
           <t>APOLO</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1185,6 +1406,11 @@
           <t>AQUARIUS - BARRA</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1202,6 +1428,11 @@
           <t>AQUARIUS - BOTAFOGO</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1219,6 +1450,11 @@
           <t>ARACARY</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1236,6 +1472,11 @@
           <t>ARAUJO LIMA</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1253,6 +1494,11 @@
           <t>ARCO</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1270,6 +1516,11 @@
           <t>ARGENTINA</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1287,6 +1538,11 @@
           <t>ARGOS COPACABANA</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1304,6 +1560,11 @@
           <t>ARLETE DONNON</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1321,6 +1582,11 @@
           <t>ARMON</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1338,6 +1604,11 @@
           <t>ARTHUR ARARIPE JUNIOR</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1355,6 +1626,11 @@
           <t>ASS AMIGOS PARC DES PALMIERS</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1372,6 +1648,11 @@
           <t>ASS MOR JARDIM PEDRA BRANCA</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1389,6 +1670,11 @@
           <t>ASS MOR L VIVENDAS DO RECREIO</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1406,6 +1692,11 @@
           <t>ASS MOR POR ADESAO RIO MAR V</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1423,6 +1714,7 @@
           <t>ASS MOR VIVENDAS DO SOL</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1440,6 +1732,11 @@
           <t>ASS MORADORES JARDIM ITANHANGA</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1457,6 +1754,11 @@
           <t>ASS RIO MAR I</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1474,6 +1776,11 @@
           <t>ASSOC DOS MORADORES RIO MAR IV</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1491,6 +1798,11 @@
           <t>ASSOC DOS MORADORES RIO MAR IX</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1508,6 +1820,11 @@
           <t>ASSOC DOS MORADORES RIO MAR X</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1525,6 +1842,11 @@
           <t>ASSOC MOR RES DON JOSE II</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1542,6 +1864,7 @@
           <t>ASSOC MORAD ALTO HUMAITA- AMAH</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1559,6 +1882,11 @@
           <t>ASSOC MORADORES RIO MAR VI</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1576,6 +1904,11 @@
           <t>ASSOCIACAO ALTO JOA</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1593,6 +1926,11 @@
           <t>ASSOCIAÇÃO MORADORES CONDADO DE YORK</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1610,6 +1948,11 @@
           <t>ASTORIA</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1627,6 +1970,11 @@
           <t>AUGUSTO ARAGAO</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1644,6 +1992,11 @@
           <t>AUSTRALIA</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1661,6 +2014,11 @@
           <t>AV EPITACIO PESSOA</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1678,6 +2036,11 @@
           <t>AVRO</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1695,6 +2058,11 @@
           <t>BAHIDJA</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1712,6 +2080,11 @@
           <t>BALTAR</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1729,6 +2102,11 @@
           <t>BAMBINA</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1746,6 +2124,11 @@
           <t>BANDEIRANTE BORBA GATO</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1763,6 +2146,11 @@
           <t>BANDEIRANTE CAPITÃO FRANCISCO PEREIRA</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1780,6 +2168,11 @@
           <t>BANDEIRANTE FRANCISCO BUENO</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1797,6 +2190,11 @@
           <t>BARAO DA TORRE II</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1814,6 +2212,11 @@
           <t>BARAO DE ITAMBI</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1831,6 +2234,11 @@
           <t>BARAO DE ITAPETININGA</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1848,6 +2256,11 @@
           <t>BARATA RIBEIRO</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1865,6 +2278,11 @@
           <t>BARRA ACRÓPOLE</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1882,6 +2300,11 @@
           <t>BARRA SOLEIL RESIDENCE</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1899,6 +2322,11 @@
           <t>BARRA WAVE RESIDENCE CLUBE</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1916,6 +2344,11 @@
           <t>BARÃO DE IPANEMA</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1933,6 +2366,11 @@
           <t>BELACAP</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1950,6 +2388,11 @@
           <t>BELAIR</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1967,6 +2410,11 @@
           <t>BELEM RIO</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1984,6 +2432,11 @@
           <t>BELMAR</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2001,6 +2454,11 @@
           <t>BELVUE</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2018,6 +2476,11 @@
           <t>BISAO</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2035,6 +2498,11 @@
           <t>BOA ESPERANCA</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2052,6 +2520,11 @@
           <t>BOGOTA</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2069,6 +2542,11 @@
           <t>BOLIVAR 35</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2086,6 +2564,11 @@
           <t>BONANCA</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2103,6 +2586,11 @@
           <t>BONAPARTE ELDORADO I II</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2120,6 +2608,11 @@
           <t>BONFIM</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2137,6 +2630,11 @@
           <t>BONFIM 155</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2154,6 +2652,11 @@
           <t>BORA BORA</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2171,6 +2674,11 @@
           <t>BORUCH BEJGEL</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2188,6 +2696,11 @@
           <t>BOTAFOGO OGGI</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2205,6 +2718,11 @@
           <t>BOTTICELLI</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2222,6 +2740,11 @@
           <t>BRASIL</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2239,6 +2762,11 @@
           <t>BROADWAY</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2256,6 +2784,11 @@
           <t>BRONX</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2273,6 +2806,11 @@
           <t>CAICO</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2290,6 +2828,11 @@
           <t>CAILLET</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2307,6 +2850,11 @@
           <t>CAIOBA</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2324,6 +2872,11 @@
           <t>CAMINO REAL</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2341,6 +2894,11 @@
           <t>CAMIZAO</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2358,6 +2916,11 @@
           <t>CAMPO DE LILLY</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2375,6 +2938,11 @@
           <t>CAMPOMAR</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2392,6 +2960,11 @@
           <t>CAMPOS SALES</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2409,6 +2982,7 @@
           <t>CANADA</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2426,6 +3000,11 @@
           <t>CANOVA</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2443,6 +3022,11 @@
           <t>CARELLI</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2460,6 +3044,11 @@
           <t>CARLOS CHAGAS</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2477,6 +3066,11 @@
           <t>CARLOS VILLAR</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2494,6 +3088,11 @@
           <t>CARMAGIL</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2511,6 +3110,11 @@
           <t>CARMEL</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2528,6 +3132,11 @@
           <t>CARMELO</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2545,6 +3154,11 @@
           <t>CARMEM</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2562,6 +3176,11 @@
           <t>CARMEM D ALMEIDA</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2579,6 +3198,7 @@
           <t>CARUARU</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2596,6 +3216,11 @@
           <t>CASA DOS OITIS</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2613,6 +3238,11 @@
           <t>CASABLANCA</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2630,6 +3260,11 @@
           <t>CASIMIRO MONTENEGRO</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2647,6 +3282,11 @@
           <t>CASTALIA</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2664,6 +3304,11 @@
           <t>CASTEL SAINT ANGELO</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2681,6 +3326,11 @@
           <t>CASTELNUOVO</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2698,6 +3348,11 @@
           <t>CATALINA</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2715,6 +3370,11 @@
           <t>CEARA</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2732,6 +3392,11 @@
           <t>CECI</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2749,6 +3414,11 @@
           <t>CELESTE</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2766,6 +3436,11 @@
           <t>CELESTER</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2783,6 +3458,11 @@
           <t>CELINA</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2800,6 +3480,11 @@
           <t>CENTRAL COPACABANA SHOPPING 680</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2817,6 +3502,11 @@
           <t>CENTRO COM CONDE DE BONFIM</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2834,6 +3524,11 @@
           <t>CENTRO COM CONDE DE BONFIM RES</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2851,6 +3546,11 @@
           <t>CENTRO COMÉRCIO JARDIM COPACABANA</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2868,6 +3568,11 @@
           <t>CENTRO DE COPACABANA</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2885,6 +3590,11 @@
           <t>CENTRO EMPRESARIAL MADUREIRA</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2902,6 +3612,11 @@
           <t>CENTRO EMPRESARIAL MARTINELLI</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2919,6 +3634,11 @@
           <t>CENTRO PROF COPE I</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2936,6 +3656,11 @@
           <t>CERRO CORA</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2953,6 +3678,11 @@
           <t>CHAMONIX</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2970,6 +3700,11 @@
           <t>CHAMONIX BOTAFOGO</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2987,6 +3722,11 @@
           <t>CHAMONIX I</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3004,6 +3744,11 @@
           <t>CHARLES ASTOR</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3021,6 +3766,11 @@
           <t>CHARLES CHAPLIN</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3038,6 +3788,11 @@
           <t>CHATEAU D AMPIERRE</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3055,6 +3810,11 @@
           <t>CHATEAU DE CHANTILLY</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3072,6 +3832,11 @@
           <t>CHATEAU DE CHAUMONT</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3089,6 +3854,11 @@
           <t>CHATEAU DE GRIGNON</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3106,6 +3876,11 @@
           <t>CHATEAU FLEURY</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3123,6 +3898,11 @@
           <t>CHATEAU FONTAINEBLEAU</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3140,6 +3920,11 @@
           <t>CLARION</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3157,6 +3942,11 @@
           <t>CLAUDE LORRAINE</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3174,6 +3964,11 @@
           <t>CLAUDIA</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3191,6 +3986,11 @@
           <t>CLICHY</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3208,6 +4008,11 @@
           <t>CLIRIAN</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3225,6 +4030,11 @@
           <t>COLUMBUS</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3242,6 +4052,11 @@
           <t>COMERCIAL NOSSA SRA COPACABANA</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3259,6 +4074,11 @@
           <t>COMMANDER</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3276,6 +4096,11 @@
           <t>COND G DO PARQUE AM DO NORTE</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3293,6 +4118,11 @@
           <t>COND IND E COM XEREM</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3310,6 +4140,11 @@
           <t>COND. ITAIPAVA - GÁVEA</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3327,6 +4162,11 @@
           <t>CONDE D'ISARON</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3344,6 +4184,11 @@
           <t>CONDE DA GAVEA</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3361,6 +4206,11 @@
           <t>CONDE DE VALMONT</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3378,6 +4228,11 @@
           <t>CONSTANTE RAMOS</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3395,6 +4250,11 @@
           <t>COPA SUL</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3412,6 +4272,11 @@
           <t>COPAMAR</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3429,6 +4294,11 @@
           <t>COSENTINO</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3446,6 +4316,11 @@
           <t>COSTA BRAVA</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3463,6 +4338,7 @@
           <t>COSTA DEL SOL</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3480,6 +4356,11 @@
           <t>COSTA VERDE - BARRA</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3497,6 +4378,11 @@
           <t>COTE D AZUR</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3514,6 +4400,11 @@
           <t>CUMPLIDO DE SANT ANNA</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3531,6 +4422,11 @@
           <t>DA PRAÇA</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3548,6 +4444,11 @@
           <t>DA RUA LEBLON</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3565,6 +4466,11 @@
           <t>DAKAR</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3582,6 +4488,11 @@
           <t>DALAMBERT</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3599,6 +4510,11 @@
           <t>DALIA</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3616,6 +4532,11 @@
           <t>DAMERIQUE</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3633,6 +4554,11 @@
           <t>DAN</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3650,6 +4576,11 @@
           <t>DAS ACCACIAS</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3667,6 +4598,11 @@
           <t>DECIO VILARES</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3684,6 +4620,11 @@
           <t>DEL MARE</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3701,6 +4642,11 @@
           <t>DELPHINUS</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3718,6 +4664,11 @@
           <t>DELTA OFFICE</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3735,6 +4686,11 @@
           <t>DESEMB COLLARES MOREIRA</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3752,6 +4708,11 @@
           <t>DESEMBARGADOR PAULO ALONSO</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3769,6 +4730,11 @@
           <t>DEZENOVE DE JANEIRO</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3786,6 +4752,11 @@
           <t>DEZESSETE DE FEVEREIRO</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3803,6 +4774,11 @@
           <t>DIDEROT</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3820,6 +4796,11 @@
           <t>DIVA</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3837,6 +4818,11 @@
           <t>DOIS IRMÃOS</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3854,6 +4840,11 @@
           <t>DOM FERNANDO</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3871,6 +4862,11 @@
           <t>DOM GUARACY</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3888,6 +4884,11 @@
           <t>DOM POLICARPO</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3905,6 +4906,11 @@
           <t>DOM RENATO</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3922,6 +4928,11 @@
           <t>DOMUS</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3939,6 +4950,11 @@
           <t>DOMUS ROMULI</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3956,6 +4972,11 @@
           <t>DONA ROMANA</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3973,6 +4994,11 @@
           <t>DONATELLO</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3990,6 +5016,11 @@
           <t>DOS ARCOS</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4007,6 +5038,11 @@
           <t>DOS DEZ</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4024,6 +5060,11 @@
           <t>DOUGLAS</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4041,6 +5082,11 @@
           <t>DOUTOR JOSÉ COHEN</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4058,6 +5104,11 @@
           <t>DULCE ORTIZ</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4075,6 +5126,11 @@
           <t>DUPERRON MADEIRA</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4092,6 +5148,11 @@
           <t>DUQUE DE TREVILLE</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4109,6 +5170,11 @@
           <t>EDELWEIS</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4126,6 +5192,11 @@
           <t>EDISON</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4143,6 +5214,11 @@
           <t>ELARA</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4160,6 +5236,11 @@
           <t>ELECTRA</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4177,6 +5258,11 @@
           <t>ELEONOR</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4194,6 +5280,11 @@
           <t>ELIZABETH</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4211,6 +5302,11 @@
           <t>ELY</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4228,6 +5324,11 @@
           <t>EMBAIXADOR OSCAR CORREA</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4245,6 +5346,11 @@
           <t>EMBAIXADOR OSWALDO ARANHA</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4262,6 +5368,11 @@
           <t>ERNESTINA MEDEIROS II</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4279,6 +5390,11 @@
           <t>EROS</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4296,6 +5412,11 @@
           <t>ESCORPIOS</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4313,6 +5434,11 @@
           <t>ESMERALDA TIJUCA</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4330,6 +5456,11 @@
           <t>ESMERALDINA</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4347,6 +5478,11 @@
           <t>ESPERANCA</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4364,6 +5500,11 @@
           <t>ESPERANÇA VILA ISABEL</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4381,6 +5522,11 @@
           <t>ESTANCIA REAL</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4398,6 +5544,11 @@
           <t>ESTORIL</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4415,6 +5566,11 @@
           <t>ESTRELA DA LAGOA</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4432,6 +5588,11 @@
           <t>FABIUS</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4449,6 +5610,11 @@
           <t>FARNESE</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4466,6 +5632,11 @@
           <t>FERREIRA DA ROSA</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4483,6 +5654,11 @@
           <t>FERREIRA PONTES</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4500,6 +5676,11 @@
           <t>FIORENZA</t>
         </is>
       </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4517,6 +5698,11 @@
           <t>FLAMENGO PARK</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4534,6 +5720,11 @@
           <t>FLAVIA</t>
         </is>
       </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4551,6 +5742,11 @@
           <t>FLAVIO JUNIOR</t>
         </is>
       </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4568,6 +5764,11 @@
           <t>FLOR DE CACTUS</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4585,6 +5786,11 @@
           <t>FLORAMAR</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4602,6 +5808,11 @@
           <t>FRANCISCO JOSE</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4619,6 +5830,11 @@
           <t>FRANCISCO SA TREZE</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4636,6 +5852,11 @@
           <t>FRANCOIS VILLON</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4653,6 +5874,11 @@
           <t>FRAZAO DE LIMA</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4670,6 +5896,11 @@
           <t>FRIBOURG</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4687,6 +5918,11 @@
           <t>GABINO</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4704,6 +5940,11 @@
           <t>GABRIELA</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4721,6 +5962,11 @@
           <t>GAL JOSE MEIRA VASCONCELOS</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4738,6 +5984,11 @@
           <t>GALAXIA</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4755,6 +6006,11 @@
           <t>GALERIA ASTOR</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4772,6 +6028,11 @@
           <t>GALERIA COMERCIAL BARVINTE</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4789,6 +6050,7 @@
           <t>GALERIA FELISBERTO DE MENEZES</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4806,6 +6068,11 @@
           <t>GALERIA TRIANGULAR</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4823,6 +6090,11 @@
           <t>GAN</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4840,6 +6112,11 @@
           <t>GENARO</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4857,6 +6134,11 @@
           <t>GENERAL PILLAR</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4874,6 +6156,11 @@
           <t>GENERAL SEVERIANO</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4891,6 +6178,11 @@
           <t>GENEVE</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4908,6 +6200,11 @@
           <t>GEREMOABO</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4925,6 +6222,11 @@
           <t>GERMANO</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4942,6 +6244,11 @@
           <t>GEZILDA</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4959,6 +6266,11 @@
           <t>GIAN</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4976,6 +6288,11 @@
           <t>GIARDINO DI FIORE</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -4993,6 +6310,11 @@
           <t>GISELLE</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5010,6 +6332,11 @@
           <t>GLAMOUR</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5027,6 +6354,11 @@
           <t>GLORY GRACE</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5044,6 +6376,11 @@
           <t>GOLD STAR</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5061,6 +6398,11 @@
           <t>GOLFO DO MEXICO</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5078,6 +6420,11 @@
           <t>GOMPAR</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5095,6 +6442,11 @@
           <t>GRAND CHARLES</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5112,6 +6464,7 @@
           <t>GREEN GARDEN</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5129,6 +6482,11 @@
           <t>GRENOBLE</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5146,6 +6504,11 @@
           <t>GUAHYRA</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5163,6 +6526,11 @@
           <t>GUSTAVE DORE</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5180,6 +6548,11 @@
           <t>HAITI</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5197,6 +6570,11 @@
           <t>HALLEY</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5214,6 +6592,11 @@
           <t>HEBE</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5231,6 +6614,11 @@
           <t>HEL VETIA</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5248,6 +6636,11 @@
           <t>HELYDE</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5265,6 +6658,11 @@
           <t>HOMEM DE MELO</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5282,6 +6680,11 @@
           <t>HONORIO LIMA</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5299,6 +6702,11 @@
           <t>HORTO FLORESTAL</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5316,6 +6724,11 @@
           <t>HOTEL RESIDENCIA SAINT PAUL</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5333,6 +6746,11 @@
           <t>HYDRA CLUBE DE MORAR</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5350,6 +6768,11 @@
           <t>IBERTIOGA</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5367,6 +6790,11 @@
           <t>IGARITE</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5384,6 +6812,11 @@
           <t>ILHA DE GRAND CAYMAN</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5401,6 +6834,11 @@
           <t>INAJA</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5418,6 +6856,11 @@
           <t>INFANTE DOM FELIPE I I I</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5435,6 +6878,11 @@
           <t>INFANTE DOM PEDRO I</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5452,6 +6900,11 @@
           <t>INTERLAKEN</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5469,6 +6922,11 @@
           <t>INTERPRISE</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5486,6 +6944,11 @@
           <t>IPAMAR II</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5503,6 +6966,11 @@
           <t>IPANEMA FRONT BEACH</t>
         </is>
       </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5520,6 +6988,11 @@
           <t>IRAPURU</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5537,6 +7010,11 @@
           <t>IRARA</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5554,6 +7032,11 @@
           <t>IRIS ELENA</t>
         </is>
       </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5571,6 +7054,11 @@
           <t>ITAGIBA</t>
         </is>
       </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5588,6 +7076,11 @@
           <t>ITAGUASSU</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5605,6 +7098,11 @@
           <t>ITAIPAVA - LEOPOLDO MIGUEZ</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5622,6 +7120,11 @@
           <t>ITAJAHI</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5639,6 +7142,11 @@
           <t>ITAPACORÁ</t>
         </is>
       </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5656,6 +7164,11 @@
           <t>ITAQUI</t>
         </is>
       </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5673,6 +7186,11 @@
           <t>JAB I</t>
         </is>
       </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5690,6 +7208,11 @@
           <t>JAB II</t>
         </is>
       </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5707,6 +7230,11 @@
           <t>JAKUY</t>
         </is>
       </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5724,6 +7252,11 @@
           <t>JAMES REBECCHI OSBORNE</t>
         </is>
       </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5741,6 +7274,11 @@
           <t>JAQUELINE</t>
         </is>
       </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5758,6 +7296,11 @@
           <t>JARDIM AMAZONAS</t>
         </is>
       </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -5775,6 +7318,11 @@
           <t>JARDIM DAS TULIPAS</t>
         </is>
       </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5792,6 +7340,11 @@
           <t>JARDIM DOS ACANTUS</t>
         </is>
       </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5809,6 +7362,11 @@
           <t>JARDIM DOS OITIS</t>
         </is>
       </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5826,6 +7384,11 @@
           <t>JARDIM LEBLON</t>
         </is>
       </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5843,6 +7406,11 @@
           <t>JARDIM RIACHUELO</t>
         </is>
       </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5860,6 +7428,11 @@
           <t>JAVA</t>
         </is>
       </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5877,6 +7450,11 @@
           <t>JOAO BRAS</t>
         </is>
       </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5894,6 +7472,11 @@
           <t>JOAQUIM NABUCO</t>
         </is>
       </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5911,6 +7494,11 @@
           <t>JOAQUIM NABUCO II</t>
         </is>
       </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -5928,6 +7516,11 @@
           <t>JOSE LUIZ FERRAZ</t>
         </is>
       </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5945,6 +7538,11 @@
           <t>JOSSAD</t>
         </is>
       </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5962,6 +7560,11 @@
           <t>JOÃO PAULO II</t>
         </is>
       </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5979,6 +7582,11 @@
           <t>JULIANA</t>
         </is>
       </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -5996,6 +7604,11 @@
           <t>JULIMAR</t>
         </is>
       </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6013,6 +7626,11 @@
           <t>JULIO COACY PEREIRA</t>
         </is>
       </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6030,6 +7648,11 @@
           <t>JUMAR</t>
         </is>
       </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6047,6 +7670,11 @@
           <t>JURUA</t>
         </is>
       </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -6064,6 +7692,11 @@
           <t>KINERET</t>
         </is>
       </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6081,6 +7714,11 @@
           <t>KING DAVID</t>
         </is>
       </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6098,6 +7736,11 @@
           <t>KING GEORGE</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6115,6 +7758,11 @@
           <t>KLOSTERS</t>
         </is>
       </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6132,6 +7780,11 @@
           <t>LA ROCHELLE</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6149,6 +7802,11 @@
           <t>LABRE</t>
         </is>
       </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6166,6 +7824,11 @@
           <t>LAFAYETTE</t>
         </is>
       </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6183,6 +7846,11 @@
           <t>LAGO MAGGIORE</t>
         </is>
       </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6200,6 +7868,11 @@
           <t>LAGOA FORMOSA E LAGOA PRATEADA</t>
         </is>
       </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6217,6 +7890,11 @@
           <t>LAILA</t>
         </is>
       </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6234,6 +7912,11 @@
           <t>LATINO</t>
         </is>
       </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6251,6 +7934,11 @@
           <t>LAURA LOTT</t>
         </is>
       </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6268,6 +7956,11 @@
           <t>LAVOURA</t>
         </is>
       </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6285,6 +7978,11 @@
           <t>LEAO VILLELA</t>
         </is>
       </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6302,6 +8000,11 @@
           <t>LENE</t>
         </is>
       </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6319,6 +8022,11 @@
           <t>LEOPOLDO MIGUEZ</t>
         </is>
       </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6336,6 +8044,11 @@
           <t>LIBANO</t>
         </is>
       </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6353,6 +8066,11 @@
           <t>LIBERAL</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6370,6 +8088,11 @@
           <t>LIEGE</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6387,6 +8110,11 @@
           <t>LINDO PARQUE II</t>
         </is>
       </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6404,6 +8132,11 @@
           <t>LOBO</t>
         </is>
       </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6421,6 +8154,11 @@
           <t>LONDRES</t>
         </is>
       </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6438,6 +8176,11 @@
           <t>LORD</t>
         </is>
       </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6455,6 +8198,11 @@
           <t>LORD TENNYSON</t>
         </is>
       </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6472,6 +8220,11 @@
           <t>LOURDES</t>
         </is>
       </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6489,6 +8242,11 @@
           <t>LUDIMILA</t>
         </is>
       </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6506,6 +8264,11 @@
           <t>LUNA</t>
         </is>
       </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6523,6 +8286,11 @@
           <t>LUX</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6540,6 +8308,11 @@
           <t>MACABEUS</t>
         </is>
       </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6557,6 +8330,11 @@
           <t>MACHOI</t>
         </is>
       </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6574,6 +8352,11 @@
           <t>MAESTRO FRANCISCO BRAGA</t>
         </is>
       </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6591,6 +8374,11 @@
           <t>MAESTRO FRANCISCO BRAGA I I I</t>
         </is>
       </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6608,6 +8396,11 @@
           <t>MAESTRO FRANCISCO BRAGA II</t>
         </is>
       </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -6625,6 +8418,11 @@
           <t>MAGALY</t>
         </is>
       </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -6642,6 +8440,11 @@
           <t>MAISON D'OR</t>
         </is>
       </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -6659,6 +8462,11 @@
           <t>MAISON DU LAC</t>
         </is>
       </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -6676,6 +8484,11 @@
           <t>MAISON REAL</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -6693,6 +8506,11 @@
           <t>MAJAH</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -6710,6 +8528,11 @@
           <t>MANACÁ</t>
         </is>
       </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -6727,6 +8550,11 @@
           <t>MANHATTAN</t>
         </is>
       </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -6744,6 +8572,11 @@
           <t>MANOEL LEITAO, 35</t>
         </is>
       </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -6761,6 +8594,11 @@
           <t>MANSAO VISCONDE DE CARAVELAS</t>
         </is>
       </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -6778,6 +8616,11 @@
           <t>MANSOES D ARAGUAIA</t>
         </is>
       </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -6795,6 +8638,11 @@
           <t>MAR AZUL</t>
         </is>
       </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -6812,6 +8660,11 @@
           <t>MAR DE VENUS</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6829,6 +8682,11 @@
           <t>MAR SERENO</t>
         </is>
       </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6846,6 +8704,11 @@
           <t>MARACA</t>
         </is>
       </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6863,6 +8726,11 @@
           <t>MARANATA</t>
         </is>
       </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6880,6 +8748,11 @@
           <t>MARAPE</t>
         </is>
       </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -6897,6 +8770,11 @@
           <t>MARCIA</t>
         </is>
       </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -6914,6 +8792,11 @@
           <t>MARCILIA</t>
         </is>
       </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -6931,6 +8814,11 @@
           <t>MARCO PAULO FRANCO</t>
         </is>
       </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -6948,6 +8836,11 @@
           <t>MARECHAL HORTA BARBOSA</t>
         </is>
       </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -6965,6 +8858,11 @@
           <t>MARGUERITE</t>
         </is>
       </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -6982,6 +8880,11 @@
           <t>MARIA ALICE</t>
         </is>
       </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -6999,6 +8902,11 @@
           <t>MARIA CELIA</t>
         </is>
       </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7016,6 +8924,11 @@
           <t>MARIA CLAUDIA</t>
         </is>
       </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7033,6 +8946,11 @@
           <t>MARIA DO CARMO</t>
         </is>
       </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7050,6 +8968,11 @@
           <t>MARIA JOSE</t>
         </is>
       </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7067,6 +8990,11 @@
           <t>MARIA LUIZA</t>
         </is>
       </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7084,6 +9012,11 @@
           <t>MARIA LUIZA I</t>
         </is>
       </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -7101,6 +9034,11 @@
           <t>MARIA SYLVIA</t>
         </is>
       </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -7118,6 +9056,11 @@
           <t>MARIA VITÓRIA</t>
         </is>
       </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7135,6 +9078,11 @@
           <t>MARILDA</t>
         </is>
       </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7152,6 +9100,11 @@
           <t>MARILIA</t>
         </is>
       </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -7169,6 +9122,11 @@
           <t>MARIMAR</t>
         </is>
       </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -7186,6 +9144,11 @@
           <t>MARINA</t>
         </is>
       </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -7203,6 +9166,11 @@
           <t>MARIPA</t>
         </is>
       </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -7220,6 +9188,11 @@
           <t>MARLUZA</t>
         </is>
       </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -7237,6 +9210,11 @@
           <t>MARQUES DE SABARA</t>
         </is>
       </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -7254,6 +9232,11 @@
           <t>MARSEILLE</t>
         </is>
       </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -7271,6 +9254,11 @@
           <t>MARTIN VAZ</t>
         </is>
       </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -7288,6 +9276,11 @@
           <t>MARTINICA</t>
         </is>
       </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -7305,6 +9298,11 @@
           <t>MARULHOS</t>
         </is>
       </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -7322,6 +9320,11 @@
           <t>MASCARENHAS DE MORAES</t>
         </is>
       </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -7339,6 +9342,11 @@
           <t>MASSET</t>
         </is>
       </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -7356,6 +9364,11 @@
           <t>MASTER</t>
         </is>
       </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -7373,6 +9386,11 @@
           <t>MATRIZ DA LAGOA</t>
         </is>
       </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -7390,6 +9408,11 @@
           <t>MEDITERRANEO SUL</t>
         </is>
       </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7407,6 +9430,11 @@
           <t>MENESCAL</t>
         </is>
       </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7424,6 +9452,11 @@
           <t>MERCEDES DE ABREU</t>
         </is>
       </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7441,6 +9474,11 @@
           <t>MESTRE JOAO</t>
         </is>
       </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7458,6 +9496,11 @@
           <t>MEUS NETINHOS</t>
         </is>
       </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7475,6 +9518,11 @@
           <t>MIGUEL ANGEL ASTURIAS</t>
         </is>
       </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7492,6 +9540,11 @@
           <t>MINDELO</t>
         </is>
       </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7509,6 +9562,11 @@
           <t>MINHA PRAIA I</t>
         </is>
       </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -7526,6 +9584,11 @@
           <t>MINISTER</t>
         </is>
       </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -7543,6 +9606,11 @@
           <t>MINISTRO NAPOLEAO REIS</t>
         </is>
       </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7560,6 +9628,11 @@
           <t>MINISTRO SALGADO FILHO</t>
         </is>
       </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -7577,6 +9650,11 @@
           <t>MIRA SERRA</t>
         </is>
       </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -7594,6 +9672,11 @@
           <t>MIRAFLORES</t>
         </is>
       </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -7611,6 +9694,11 @@
           <t>MIRANTE</t>
         </is>
       </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -7628,6 +9716,11 @@
           <t>MIRIAN</t>
         </is>
       </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -7645,6 +9738,11 @@
           <t>MITHRA</t>
         </is>
       </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -7662,6 +9760,11 @@
           <t>MODULO II</t>
         </is>
       </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -7679,6 +9782,11 @@
           <t>MONA LISA</t>
         </is>
       </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -7696,6 +9804,11 @@
           <t>MONACO</t>
         </is>
       </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -7713,6 +9826,11 @@
           <t>MONDESIR</t>
         </is>
       </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -7730,6 +9848,11 @@
           <t>MONSARAZ</t>
         </is>
       </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -7747,6 +9870,11 @@
           <t>MONTANHES</t>
         </is>
       </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -7764,6 +9892,11 @@
           <t>MONTE BELO</t>
         </is>
       </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -7781,6 +9914,11 @@
           <t>MONTE CARLO</t>
         </is>
       </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -7798,6 +9936,11 @@
           <t>MONTE HATIRA</t>
         </is>
       </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -7815,6 +9958,11 @@
           <t>MONTE SAMEIRO</t>
         </is>
       </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -7832,6 +9980,11 @@
           <t>MONTENEGRO 121</t>
         </is>
       </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -7849,6 +10002,11 @@
           <t>MONTESANO</t>
         </is>
       </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -7866,6 +10024,11 @@
           <t>MONTEVERDE</t>
         </is>
       </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -7883,6 +10046,11 @@
           <t>MONTEVIDEO</t>
         </is>
       </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -7900,6 +10068,11 @@
           <t>MONTPELLIER</t>
         </is>
       </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -7917,6 +10090,11 @@
           <t>MORADA LAGOAMAR</t>
         </is>
       </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -7934,6 +10112,11 @@
           <t>MOZART</t>
         </is>
       </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -7951,6 +10134,11 @@
           <t>MURIAE</t>
         </is>
       </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -7968,6 +10156,11 @@
           <t>MY FLOWER</t>
         </is>
       </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -7985,6 +10178,11 @@
           <t>NATALIA</t>
         </is>
       </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -8002,6 +10200,11 @@
           <t>NEGRESCO</t>
         </is>
       </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -8019,6 +10222,11 @@
           <t>NEGRESCO IPANEMA</t>
         </is>
       </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -8036,6 +10244,11 @@
           <t>NICOLE</t>
         </is>
       </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -8053,6 +10266,11 @@
           <t>NOA NOA</t>
         </is>
       </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8070,6 +10288,11 @@
           <t>NOAMA</t>
         </is>
       </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8087,6 +10310,11 @@
           <t>NOBRE DE EVORA</t>
         </is>
       </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -8104,6 +10332,11 @@
           <t>NOBRE DE SAGRES</t>
         </is>
       </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -8121,6 +10354,11 @@
           <t>NOBREZA</t>
         </is>
       </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -8138,6 +10376,11 @@
           <t>NORTE</t>
         </is>
       </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -8155,6 +10398,11 @@
           <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -8172,6 +10420,11 @@
           <t>NOSSA SENHORA DE NAZARETH</t>
         </is>
       </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -8189,6 +10442,11 @@
           <t>NOVA OLINDA</t>
         </is>
       </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -8206,6 +10464,11 @@
           <t>NOVO VALE</t>
         </is>
       </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -8223,6 +10486,11 @@
           <t>OASIS</t>
         </is>
       </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -8240,6 +10508,11 @@
           <t>OCTACILIO GUALBERTO DE OLIVEIR</t>
         </is>
       </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -8257,6 +10530,11 @@
           <t>ODEON</t>
         </is>
       </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -8274,6 +10552,11 @@
           <t>OIANA</t>
         </is>
       </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -8291,6 +10574,11 @@
           <t>OLIVANIA</t>
         </is>
       </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -8308,6 +10596,11 @@
           <t>OLYNTHO RIBEIRO</t>
         </is>
       </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -8325,6 +10618,11 @@
           <t>OPUS VERDI</t>
         </is>
       </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -8342,6 +10640,11 @@
           <t>OURO VERDE</t>
         </is>
       </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -8359,6 +10662,11 @@
           <t>OURO VERDE I</t>
         </is>
       </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -8376,6 +10684,11 @@
           <t>PAIVA</t>
         </is>
       </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -8393,6 +10706,11 @@
           <t>PALACE</t>
         </is>
       </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -8410,6 +10728,11 @@
           <t>PALACETE SAO JOAO D EL REY</t>
         </is>
       </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -8427,6 +10750,11 @@
           <t>PALACETE SÃO PAULO</t>
         </is>
       </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -8444,6 +10772,11 @@
           <t>PALACETE VEIGA</t>
         </is>
       </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -8461,6 +10794,11 @@
           <t>PALACIO ALVORADA</t>
         </is>
       </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8478,6 +10816,11 @@
           <t>PALAZZO CRISTALLO</t>
         </is>
       </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -8495,6 +10838,11 @@
           <t>PALAZZO DEI VISCONTI</t>
         </is>
       </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8512,6 +10860,11 @@
           <t>PALAZZO PITTI</t>
         </is>
       </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -8529,6 +10882,11 @@
           <t>PALMEIRA DE SARANDY</t>
         </is>
       </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -8546,6 +10904,11 @@
           <t>PANCETTI</t>
         </is>
       </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -8563,6 +10926,11 @@
           <t>PARK URUGUAY</t>
         </is>
       </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -8580,6 +10948,11 @@
           <t>PARQ RES DAYSE LUCY BOLELLI</t>
         </is>
       </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -8597,6 +10970,11 @@
           <t>PARQUE AMERICA DO SUL</t>
         </is>
       </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -8614,6 +10992,11 @@
           <t>PARQUE JARDIM EUROPA</t>
         </is>
       </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -8631,6 +11014,11 @@
           <t>PASTEUR</t>
         </is>
       </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -8648,6 +11036,11 @@
           <t>PATRICIA</t>
         </is>
       </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -8665,6 +11058,11 @@
           <t>PAULA</t>
         </is>
       </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -8682,6 +11080,11 @@
           <t>PAULA E SILVA</t>
         </is>
       </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -8699,6 +11102,11 @@
           <t>PAULINA</t>
         </is>
       </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -8716,6 +11124,11 @@
           <t>PAULINA I</t>
         </is>
       </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -8733,6 +11146,11 @@
           <t>PAULO FRAGOSO</t>
         </is>
       </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -8750,6 +11168,11 @@
           <t>PEIXOTO</t>
         </is>
       </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -8767,6 +11190,11 @@
           <t>PEIXOTO DE CASTRO</t>
         </is>
       </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -8784,6 +11212,11 @@
           <t>PENA BERILO</t>
         </is>
       </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -8801,6 +11234,11 @@
           <t>PENA BRANCA</t>
         </is>
       </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -8818,6 +11256,11 @@
           <t>PENA TURQUESA</t>
         </is>
       </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -8835,6 +11278,11 @@
           <t>PEPE BEACH EMPRESARIAL</t>
         </is>
       </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -8852,6 +11300,11 @@
           <t>PERL JUER</t>
         </is>
       </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -8869,6 +11322,11 @@
           <t>PHOENIX</t>
         </is>
       </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -8886,6 +11344,11 @@
           <t>PILOTIS</t>
         </is>
       </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -8903,6 +11366,11 @@
           <t>PINA</t>
         </is>
       </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -8920,6 +11388,11 @@
           <t>PINDORAMA</t>
         </is>
       </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -8937,6 +11410,11 @@
           <t>PINHEIROS</t>
         </is>
       </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -8954,6 +11432,11 @@
           <t>PIRAMBU</t>
         </is>
       </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -8971,6 +11454,11 @@
           <t>PIRATININGA</t>
         </is>
       </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -8988,6 +11476,11 @@
           <t>PIUS</t>
         </is>
       </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -9005,6 +11498,11 @@
           <t>POMPEU LOUREIRO</t>
         </is>
       </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -9022,6 +11520,11 @@
           <t>POMPEU LOUREIRO 39</t>
         </is>
       </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -9039,6 +11542,11 @@
           <t>PORTO DOS TAINHEIROS</t>
         </is>
       </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -9056,6 +11564,11 @@
           <t>PORTO SANTORINI</t>
         </is>
       </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -9073,6 +11586,11 @@
           <t>PRACA DE VARGEM GRANDE</t>
         </is>
       </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -9090,6 +11608,11 @@
           <t>PRACA PIO XI</t>
         </is>
       </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -9107,6 +11630,11 @@
           <t>PRAIA CATALINA</t>
         </is>
       </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -9124,6 +11652,11 @@
           <t>PRAIA DA PITUBA</t>
         </is>
       </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -9141,6 +11674,11 @@
           <t>PRAIA DE SAGRES</t>
         </is>
       </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -9158,6 +11696,11 @@
           <t>PRESIDENTE ABRAHAM LINCOLN</t>
         </is>
       </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -9175,6 +11718,11 @@
           <t>PRESIDENTE PENNA</t>
         </is>
       </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -9192,6 +11740,11 @@
           <t>PRIMAVERA II</t>
         </is>
       </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -9209,6 +11762,11 @@
           <t>PRIME VILLE</t>
         </is>
       </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -9226,6 +11784,11 @@
           <t>PRINCE GEORGE</t>
         </is>
       </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -9243,6 +11806,11 @@
           <t>PRO RIOMAR</t>
         </is>
       </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -9260,6 +11828,11 @@
           <t>PROENCA ROSA</t>
         </is>
       </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -9277,6 +11850,11 @@
           <t>PRUDENTE DE MORAES III</t>
         </is>
       </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -9294,6 +11872,11 @@
           <t>PURA</t>
         </is>
       </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -9311,6 +11894,11 @@
           <t>QUATI</t>
         </is>
       </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -9328,6 +11916,11 @@
           <t>RACHEL</t>
         </is>
       </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -9345,6 +11938,11 @@
           <t>RAIMUNDO MAGALHAES</t>
         </is>
       </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -9362,6 +11960,11 @@
           <t>RAINHA ASTRID</t>
         </is>
       </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -9379,6 +11982,11 @@
           <t>RAINHA DA PAZ</t>
         </is>
       </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -9396,6 +12004,11 @@
           <t>RAINHA ELIZABETH</t>
         </is>
       </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -9413,6 +12026,11 @@
           <t>RAUL POMPEIA</t>
         </is>
       </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -9430,6 +12048,11 @@
           <t>RAWET</t>
         </is>
       </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -9447,6 +12070,11 @@
           <t>RAYMUNDO COREOLANO CORREA</t>
         </is>
       </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -9464,6 +12092,11 @@
           <t>REAL SHOPPING</t>
         </is>
       </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -9481,6 +12114,11 @@
           <t>RECANTO DO RECREIO</t>
         </is>
       </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -9498,6 +12136,11 @@
           <t>RECANTO DOS COLIBRIS</t>
         </is>
       </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -9515,6 +12158,11 @@
           <t>RECREIO MEDICAL CENTER</t>
         </is>
       </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -9532,6 +12180,11 @@
           <t>REI ALBERTO</t>
         </is>
       </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -9549,6 +12202,11 @@
           <t>REI EDUARDO</t>
         </is>
       </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -9566,6 +12224,11 @@
           <t>RENA</t>
         </is>
       </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -9583,6 +12246,11 @@
           <t>RENOIR I</t>
         </is>
       </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -9600,6 +12268,11 @@
           <t>RESEDA</t>
         </is>
       </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -9617,6 +12290,11 @@
           <t>RESID. GUSTAV MAHLER</t>
         </is>
       </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -9634,6 +12312,11 @@
           <t>RESIDENC PASQUALE SCOFANO</t>
         </is>
       </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -9651,6 +12334,11 @@
           <t>RESIDENCIAL COSTA DO SOL</t>
         </is>
       </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -9668,6 +12356,11 @@
           <t>RESIDENCIAL CRISFLAN I</t>
         </is>
       </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -9685,6 +12378,11 @@
           <t>RESIDENCIAL HELENA</t>
         </is>
       </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -9702,6 +12400,11 @@
           <t>RESIDENCIAL MELLODY</t>
         </is>
       </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -9719,6 +12422,11 @@
           <t>RESIDENCIAL MILANO</t>
         </is>
       </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -9736,6 +12444,11 @@
           <t>RESIDENCIAL MONTMORRENCY</t>
         </is>
       </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -9753,6 +12466,11 @@
           <t>RESIDENCIAL SAN SIRO</t>
         </is>
       </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -9770,6 +12488,11 @@
           <t>RESIDENCIAL SAO FERNANDO</t>
         </is>
       </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -9787,6 +12510,11 @@
           <t>RESIDENCIAS BARRA</t>
         </is>
       </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -9804,6 +12532,11 @@
           <t>RESIDÊNCIAS LASAR SEGALL</t>
         </is>
       </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -9821,6 +12554,11 @@
           <t>RIBALTA</t>
         </is>
       </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -9838,6 +12576,11 @@
           <t>RIBEIRO DO PRADO</t>
         </is>
       </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -9855,6 +12598,11 @@
           <t>RIBOT</t>
         </is>
       </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -9872,6 +12620,11 @@
           <t>RICARDO</t>
         </is>
       </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -9889,6 +12642,11 @@
           <t>RIO DAS FLORES</t>
         </is>
       </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -9906,6 +12664,11 @@
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -9923,6 +12686,11 @@
           <t>RIO ELBA</t>
         </is>
       </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -9940,6 +12708,11 @@
           <t>RIO LIMA</t>
         </is>
       </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -9957,6 +12730,11 @@
           <t>RIO MARUPI</t>
         </is>
       </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -9974,6 +12752,11 @@
           <t>RIO NOBRE</t>
         </is>
       </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -9991,6 +12774,11 @@
           <t>RIO PALACE</t>
         </is>
       </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -10008,6 +12796,7 @@
           <t>RIO PARA</t>
         </is>
       </c>
+      <c r="D564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -10025,6 +12814,11 @@
           <t>RIO REAL</t>
         </is>
       </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -10042,6 +12836,11 @@
           <t>RIO RENO</t>
         </is>
       </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -10059,6 +12858,11 @@
           <t>RIO TAPAJOS</t>
         </is>
       </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -10076,6 +12880,11 @@
           <t>RIO TAQUARI</t>
         </is>
       </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -10093,6 +12902,11 @@
           <t>RIONER</t>
         </is>
       </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -10110,6 +12924,11 @@
           <t>RIVER</t>
         </is>
       </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -10127,6 +12946,11 @@
           <t>RIVIERA</t>
         </is>
       </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -10144,6 +12968,11 @@
           <t>ROBERT KENNEDY</t>
         </is>
       </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -10161,6 +12990,11 @@
           <t>ROCHEDO</t>
         </is>
       </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -10178,6 +13012,11 @@
           <t>RODALMA</t>
         </is>
       </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -10195,6 +13034,11 @@
           <t>RODRIGUS</t>
         </is>
       </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -10212,6 +13056,11 @@
           <t>ROSA DE BELLIS</t>
         </is>
       </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -10229,6 +13078,11 @@
           <t>ROSA VIVA</t>
         </is>
       </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -10246,6 +13100,11 @@
           <t>ROSALENI</t>
         </is>
       </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -10263,6 +13122,11 @@
           <t>ROSE MARIE</t>
         </is>
       </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -10280,6 +13144,11 @@
           <t>ROSELENE</t>
         </is>
       </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -10297,6 +13166,11 @@
           <t>ROSIG</t>
         </is>
       </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -10314,6 +13188,11 @@
           <t>ROSINA</t>
         </is>
       </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -10331,6 +13210,11 @@
           <t>ROUSSEAU</t>
         </is>
       </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -10348,6 +13232,11 @@
           <t>ROXY</t>
         </is>
       </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -10365,6 +13254,11 @@
           <t>RUA BARATA RIBEIRO 808</t>
         </is>
       </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -10382,6 +13276,11 @@
           <t>RUTH</t>
         </is>
       </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -10399,6 +13298,11 @@
           <t>RYDLAVES</t>
         </is>
       </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -10416,6 +13320,11 @@
           <t>SA FREIRE ALVIM</t>
         </is>
       </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -10433,6 +13342,11 @@
           <t>SADDOCK DE SÁ145</t>
         </is>
       </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -10450,6 +13364,11 @@
           <t>SADOC MENASCHE</t>
         </is>
       </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -10467,6 +13386,11 @@
           <t>SAINT ANGELE</t>
         </is>
       </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -10484,6 +13408,11 @@
           <t>SAINT GOTTARDO</t>
         </is>
       </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -10501,6 +13430,11 @@
           <t>SAINT MALO</t>
         </is>
       </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -10518,6 +13452,11 @@
           <t>SAINT NAZAIRE</t>
         </is>
       </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -10535,6 +13474,11 @@
           <t>SAINT PAUL</t>
         </is>
       </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -10552,6 +13496,11 @@
           <t>SALK</t>
         </is>
       </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -10569,6 +13518,11 @@
           <t>SAMARA</t>
         </is>
       </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -10586,6 +13540,11 @@
           <t>SAMOA</t>
         </is>
       </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -10603,6 +13562,11 @@
           <t>SAN DIEGO</t>
         </is>
       </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -10620,6 +13584,11 @@
           <t>SAN MICHELLI</t>
         </is>
       </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -10637,6 +13606,11 @@
           <t>SAN NICOLA</t>
         </is>
       </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -10654,6 +13628,11 @@
           <t>SAN PIETRO</t>
         </is>
       </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -10671,6 +13650,11 @@
           <t>SAN REMO</t>
         </is>
       </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -10688,6 +13672,11 @@
           <t>SAN ROSE</t>
         </is>
       </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -10705,6 +13694,11 @@
           <t>SANTA HELENA</t>
         </is>
       </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -10722,6 +13716,11 @@
           <t>SANTA HELOISA</t>
         </is>
       </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -10739,6 +13738,11 @@
           <t>SANTA INES</t>
         </is>
       </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -10756,6 +13760,11 @@
           <t>SANTA MONICA</t>
         </is>
       </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -10773,6 +13782,11 @@
           <t>SANTO ANTONIO</t>
         </is>
       </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -10790,6 +13804,11 @@
           <t>SAO DINIZ</t>
         </is>
       </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -10807,6 +13826,11 @@
           <t>SAO JUDAS TADEU</t>
         </is>
       </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -10824,6 +13848,11 @@
           <t>SAO PEDRO</t>
         </is>
       </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -10841,6 +13870,11 @@
           <t>SAO ROQUE</t>
         </is>
       </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -10858,6 +13892,11 @@
           <t>SAO TADEU</t>
         </is>
       </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -10875,6 +13914,11 @@
           <t>SARAH</t>
         </is>
       </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -10892,6 +13936,11 @@
           <t>SARGO</t>
         </is>
       </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -10909,6 +13958,11 @@
           <t>SATURNO</t>
         </is>
       </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -10926,6 +13980,11 @@
           <t>SAUL PERELBERG</t>
         </is>
       </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -10943,6 +14002,11 @@
           <t>SENADOR LEITE OITICICA</t>
         </is>
       </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -10960,6 +14024,11 @@
           <t>SENCOMAR</t>
         </is>
       </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -10977,6 +14046,11 @@
           <t>SERAFIM VALANDRO</t>
         </is>
       </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -10994,6 +14068,11 @@
           <t>SERENATA</t>
         </is>
       </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -11011,6 +14090,11 @@
           <t>SERRA AZUL</t>
         </is>
       </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -11028,6 +14112,11 @@
           <t>SERRA DAS LAJES</t>
         </is>
       </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -11045,6 +14134,11 @@
           <t>SERRA E MAR DO RECREIO</t>
         </is>
       </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -11062,6 +14156,11 @@
           <t>SERRA GRANDE</t>
         </is>
       </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -11079,6 +14178,11 @@
           <t>SERRA NEGRA</t>
         </is>
       </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -11096,6 +14200,11 @@
           <t>SEVEN</t>
         </is>
       </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -11113,6 +14222,11 @@
           <t>SHANGRI LA</t>
         </is>
       </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -11130,6 +14244,11 @@
           <t>SHOPPING DA CAIXA</t>
         </is>
       </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -11147,6 +14266,11 @@
           <t>SILVER</t>
         </is>
       </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -11164,6 +14288,11 @@
           <t>SILVERSTONE</t>
         </is>
       </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -11181,6 +14310,11 @@
           <t>SIMONE</t>
         </is>
       </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -11198,6 +14332,11 @@
           <t>SINAI</t>
         </is>
       </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -11215,6 +14354,11 @@
           <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -11232,6 +14376,7 @@
           <t>SISALPAX</t>
         </is>
       </c>
+      <c r="D636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -11249,6 +14394,11 @@
           <t>SITIO ITUVERAVA</t>
         </is>
       </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -11266,6 +14416,11 @@
           <t>SITIO SANTANNA</t>
         </is>
       </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -11283,6 +14438,11 @@
           <t>SIVA</t>
         </is>
       </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -11300,6 +14460,11 @@
           <t>SOCICO</t>
         </is>
       </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -11317,6 +14482,11 @@
           <t>SOLAR</t>
         </is>
       </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -11334,6 +14504,11 @@
           <t>SOLAR CAJUTI</t>
         </is>
       </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -11351,6 +14526,11 @@
           <t>SOLAR DA LAGOA</t>
         </is>
       </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -11368,6 +14548,11 @@
           <t>SOLAR DA TIJUCA</t>
         </is>
       </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -11385,6 +14570,11 @@
           <t>SOLAR DAS ACACIAS</t>
         </is>
       </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -11402,6 +14592,11 @@
           <t>SOLAR DAS BROMELIAS</t>
         </is>
       </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -11419,6 +14614,11 @@
           <t>SOLAR DAS PALMEIRAS</t>
         </is>
       </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -11436,6 +14636,11 @@
           <t>SOLAR DE COPACABANA</t>
         </is>
       </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -11453,6 +14658,11 @@
           <t>SOLAR DE IPANEMA</t>
         </is>
       </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -11470,6 +14680,11 @@
           <t>SOLAR DO ARPOADOR</t>
         </is>
       </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -11487,6 +14702,11 @@
           <t>SOLAR DONA MARIANA</t>
         </is>
       </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -11504,6 +14724,11 @@
           <t>SOLAR DOS MANANCIAIS</t>
         </is>
       </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -11521,6 +14746,11 @@
           <t>SOLAR DOS VENTOS</t>
         </is>
       </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -11538,6 +14768,11 @@
           <t>SOLAR DUQUESA DE ALBA</t>
         </is>
       </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -11555,6 +14790,11 @@
           <t>SOLAR MARQUES DE SAO VICENTE</t>
         </is>
       </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -11572,6 +14812,11 @@
           <t>SOLAR PRINCIPE CHARLES</t>
         </is>
       </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -11589,6 +14834,11 @@
           <t>SOLAR RAINHA FABIOLA</t>
         </is>
       </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -11606,6 +14856,11 @@
           <t>SOLAR REGO LOPES</t>
         </is>
       </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -11623,6 +14878,11 @@
           <t>SOLAR VISCONDE DE MAGÉ</t>
         </is>
       </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -11640,6 +14900,11 @@
           <t>SOLAR VOLUNTARIOS DA PATRIA</t>
         </is>
       </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -11657,6 +14922,11 @@
           <t>SOSSEGO</t>
         </is>
       </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -11674,6 +14944,11 @@
           <t>SOUTH BEACH COPACABANA RESIDENCE CLUB</t>
         </is>
       </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -11691,6 +14966,11 @@
           <t>SOUZA LIMA</t>
         </is>
       </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -11708,6 +14988,11 @@
           <t>SPRING</t>
         </is>
       </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -11725,6 +15010,11 @@
           <t>STELLA SIRIUS</t>
         </is>
       </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -11742,6 +15032,11 @@
           <t>SUL ATLANTICO</t>
         </is>
       </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -11759,6 +15054,11 @@
           <t>SUMARÉ</t>
         </is>
       </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -11776,6 +15076,11 @@
           <t>SÃO LUIZ</t>
         </is>
       </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -11793,6 +15098,11 @@
           <t>SÃO RAFAEL</t>
         </is>
       </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -11810,6 +15120,11 @@
           <t>SÃO THOMÉ III</t>
         </is>
       </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -11827,6 +15142,11 @@
           <t>SÃO VICENTE</t>
         </is>
       </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -11844,6 +15164,11 @@
           <t>TAMPICO</t>
         </is>
       </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -11861,6 +15186,11 @@
           <t>TANIT</t>
         </is>
       </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -11878,6 +15208,11 @@
           <t>TARAHUMARA</t>
         </is>
       </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -11895,6 +15230,11 @@
           <t>TATIANA RODRIGUES</t>
         </is>
       </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -11912,6 +15252,11 @@
           <t>TAUNTON</t>
         </is>
       </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -11929,6 +15274,11 @@
           <t>TEBAS</t>
         </is>
       </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -11946,6 +15296,11 @@
           <t>TENENTE MARONES DE GUSMAO</t>
         </is>
       </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -11963,6 +15318,11 @@
           <t>TEREZA CRISTINA</t>
         </is>
       </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -11980,6 +15340,7 @@
           <t>TERMOLI RESIDENCE SERVICE</t>
         </is>
       </c>
+      <c r="D680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -11997,6 +15358,11 @@
           <t>TERRACAS DA BARRA</t>
         </is>
       </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -12014,6 +15380,11 @@
           <t>TIBAGI</t>
         </is>
       </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -12031,6 +15402,11 @@
           <t>TIJUCA</t>
         </is>
       </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -12048,6 +15424,11 @@
           <t>TIVOLI</t>
         </is>
       </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -12065,6 +15446,11 @@
           <t>TIZIANO</t>
         </is>
       </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -12082,6 +15468,11 @@
           <t>TODOS OS SANTOS</t>
         </is>
       </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -12099,6 +15490,11 @@
           <t>TOPAZIO</t>
         </is>
       </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -12116,6 +15512,11 @@
           <t>TOPAZIO (Barra)</t>
         </is>
       </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -12133,6 +15534,11 @@
           <t>TORRE DE BELÉM</t>
         </is>
       </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -12150,6 +15556,11 @@
           <t>TOULOUSE</t>
         </is>
       </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -12167,6 +15578,11 @@
           <t>TOUR D ARGENT</t>
         </is>
       </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -12184,6 +15600,11 @@
           <t>TOUR DE BLOIS</t>
         </is>
       </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -12201,6 +15622,11 @@
           <t>TOUR DE ROCHELLE</t>
         </is>
       </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -12218,6 +15644,11 @@
           <t>TOY</t>
         </is>
       </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -12235,6 +15666,11 @@
           <t>TRAJANO</t>
         </is>
       </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -12252,6 +15688,11 @@
           <t>TRES DE MARCO</t>
         </is>
       </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -12269,6 +15710,11 @@
           <t>TREZE DE JANEIRO</t>
         </is>
       </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -12286,6 +15732,11 @@
           <t>TUFFY NICOLAU HABIB</t>
         </is>
       </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -12303,6 +15754,11 @@
           <t>TULIPA</t>
         </is>
       </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -12320,6 +15776,11 @@
           <t>TUNEL</t>
         </is>
       </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -12337,6 +15798,11 @@
           <t>UBIRAJARA</t>
         </is>
       </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -12354,6 +15820,11 @@
           <t>UIARA</t>
         </is>
       </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -12371,6 +15842,11 @@
           <t>ULYSSEA</t>
         </is>
       </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -12388,6 +15864,11 @@
           <t>UNIAO</t>
         </is>
       </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -12405,6 +15886,11 @@
           <t>UPAHYBA</t>
         </is>
       </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -12422,6 +15908,11 @@
           <t>URCA</t>
         </is>
       </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -12439,6 +15930,11 @@
           <t>URCA VISTA-MAR</t>
         </is>
       </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -12456,6 +15952,11 @@
           <t>URIEL</t>
         </is>
       </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -12473,6 +15974,11 @@
           <t>URUCATAN</t>
         </is>
       </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -12490,6 +15996,11 @@
           <t>VAL DE LOIRE</t>
         </is>
       </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -12507,6 +16018,11 @@
           <t>VALENCA TEIXEIRA</t>
         </is>
       </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -12524,6 +16040,11 @@
           <t>VALENTE XVI</t>
         </is>
       </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -12541,6 +16062,11 @@
           <t>VALENZA</t>
         </is>
       </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -12558,6 +16084,11 @@
           <t>VARANDA DAS ROSAS</t>
         </is>
       </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -12575,6 +16106,11 @@
           <t>VARANDAS DA VILA</t>
         </is>
       </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -12592,6 +16128,11 @@
           <t>VELAS ICADAS</t>
         </is>
       </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -12609,6 +16150,11 @@
           <t>VENEZA</t>
         </is>
       </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -12626,6 +16172,11 @@
           <t>VERA CRUZ</t>
         </is>
       </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -12643,6 +16194,11 @@
           <t>VERA WAKIM ABEID</t>
         </is>
       </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -12660,6 +16216,11 @@
           <t>VERDE LEBLON</t>
         </is>
       </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -12677,6 +16238,11 @@
           <t>VERDE RASA</t>
         </is>
       </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -12694,6 +16260,11 @@
           <t>VERONICA V I I I</t>
         </is>
       </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -12711,6 +16282,11 @@
           <t>VERONICA VII</t>
         </is>
       </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -12728,6 +16304,11 @@
           <t>VIA DE MARTELLI</t>
         </is>
       </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -12745,6 +16326,11 @@
           <t>VIAREGGIO</t>
         </is>
       </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -12762,6 +16348,11 @@
           <t>VILA CANNING</t>
         </is>
       </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -12779,6 +16370,11 @@
           <t>VILA VERDE</t>
         </is>
       </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -12796,6 +16392,11 @@
           <t>VILLA BRANCA</t>
         </is>
       </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -12813,6 +16414,11 @@
           <t>VILLA DI GENOVA</t>
         </is>
       </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -12830,6 +16436,11 @@
           <t>VILLAGE SANTA AMERICA I</t>
         </is>
       </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -12847,6 +16458,11 @@
           <t>VILLARS</t>
         </is>
       </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -12864,6 +16480,11 @@
           <t>VILLE DE BEAUVAIS</t>
         </is>
       </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -12881,6 +16502,11 @@
           <t>VINA</t>
         </is>
       </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -12898,6 +16524,11 @@
           <t>VINA DEL MAR</t>
         </is>
       </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -12915,6 +16546,11 @@
           <t>VINHA NOVA</t>
         </is>
       </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -12932,6 +16568,11 @@
           <t>VINICIUS</t>
         </is>
       </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -12949,6 +16590,11 @@
           <t>VINTE E UM DE AGOSTO</t>
         </is>
       </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -12966,6 +16612,11 @@
           <t>VISCONDE DE CABO FRIO</t>
         </is>
       </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -12983,6 +16634,11 @@
           <t>VISTAMAR II</t>
         </is>
       </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -13000,6 +16656,11 @@
           <t>VITOR KONDER</t>
         </is>
       </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -13017,6 +16678,11 @@
           <t>VITORIO DA COSTA</t>
         </is>
       </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -13034,6 +16700,11 @@
           <t>VIUVA LACERDA</t>
         </is>
       </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -13051,6 +16722,11 @@
           <t>VIVEIRO DE CASTRO</t>
         </is>
       </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -13068,6 +16744,11 @@
           <t>VIVENDA DO IPÊ</t>
         </is>
       </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -13085,6 +16766,11 @@
           <t>VIVENDA ONZE</t>
         </is>
       </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -13102,6 +16788,11 @@
           <t>VIVENDAS DE MAIO</t>
         </is>
       </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -13119,6 +16810,11 @@
           <t>VIVIANE</t>
         </is>
       </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -13136,6 +16832,11 @@
           <t>VIVIEN</t>
         </is>
       </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -13153,6 +16854,11 @@
           <t>VIZA</t>
         </is>
       </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -13170,6 +16876,11 @@
           <t>VON MARTIUS</t>
         </is>
       </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -13187,6 +16898,11 @@
           <t>WALFRAN II</t>
         </is>
       </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -13204,6 +16920,11 @@
           <t>WALQUIRIA</t>
         </is>
       </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -13221,6 +16942,11 @@
           <t>WINDSOR</t>
         </is>
       </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -13238,6 +16964,11 @@
           <t>XAVIER DA SILVEIRA</t>
         </is>
       </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -13255,6 +16986,11 @@
           <t>YEMANJA</t>
         </is>
       </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -13272,6 +17008,11 @@
           <t>ZACO PARANÁ</t>
         </is>
       </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -13289,6 +17030,11 @@
           <t>ZENIA</t>
         </is>
       </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -13304,6 +17050,11 @@
       <c r="C758" t="inlineStr">
         <is>
           <t>ZULEIKA</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>797</t>
         </is>
       </c>
     </row>
